--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_MELILLA CIUDAD DEL DEPORTE.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_MELILLA CIUDAD DEL DEPORTE.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -943,28 +943,28 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>3.5392</v>
+        <v>4.1542</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7143</v>
+        <v>3.3293</v>
       </c>
       <c r="F7" t="n">
         <v>0.8248999999999995</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6765000000000001</v>
+        <v>-0.06149999999999967</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.6435</v>
+        <v>-3.0284</v>
       </c>
       <c r="I7" t="n">
         <v>2.967</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.9052</v>
+        <v>-1.2902</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.0698</v>
+        <v>-2.4548</v>
       </c>
       <c r="L7" t="n">
         <v>1.1646</v>
@@ -1087,7 +1087,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. MUÑOZ QUIÑONES</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1096,76 +1096,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.215</v>
+        <v>0.7013000000000005</v>
       </c>
       <c r="E9" t="n">
-        <v>1.215</v>
+        <v>-3.145</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3.8464</v>
       </c>
       <c r="G9" t="n">
-        <v>1.215</v>
+        <v>6.5407</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-3.9973</v>
       </c>
       <c r="I9" t="n">
-        <v>1.215</v>
+        <v>10.538</v>
       </c>
       <c r="J9" t="n">
-        <v>1.215</v>
+        <v>7.7642</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.9583</v>
       </c>
       <c r="L9" t="n">
-        <v>1.215</v>
+        <v>8.7225</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-1.2236</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-3.0391</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.8155</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-8.7742</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-16.7688</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>7.9944</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0.5664</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.5279999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-1.0943</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3.5014</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>5.3315</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.8301</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>M. STRIKKER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1174,76 +1174,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7013000000000005</v>
+        <v>0.1154</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.145</v>
+        <v>-0.5947</v>
       </c>
       <c r="F10" t="n">
-        <v>3.8464</v>
+        <v>0.7101</v>
       </c>
       <c r="G10" t="n">
-        <v>6.5407</v>
+        <v>0.452</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.9973</v>
+        <v>0.3451</v>
       </c>
       <c r="I10" t="n">
-        <v>10.538</v>
+        <v>0.1069</v>
       </c>
       <c r="J10" t="n">
-        <v>7.7642</v>
+        <v>0.316</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9583</v>
+        <v>0.3485</v>
       </c>
       <c r="L10" t="n">
-        <v>8.7225</v>
+        <v>-0.0325</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2236</v>
+        <v>0.136</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.0391</v>
+        <v>-0.0034</v>
       </c>
       <c r="O10" t="n">
-        <v>1.8155</v>
+        <v>0.1394</v>
       </c>
       <c r="P10" t="n">
-        <v>-8.7742</v>
+        <v>-0.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>-16.7688</v>
+        <v>-0.9749</v>
       </c>
       <c r="R10" t="n">
-        <v>7.9944</v>
+        <v>0.585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5664</v>
+        <v>0.0533</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5279999999999999</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0943</v>
+        <v>-0.0109</v>
       </c>
       <c r="V10" t="n">
-        <v>3.5014</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>5.3315</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,73 +1255,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.615</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.615</v>
+        <v>-2.6284</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1.8356</v>
       </c>
       <c r="G11" t="n">
-        <v>0.615</v>
+        <v>0.3481</v>
       </c>
       <c r="H11" t="n">
-        <v>0.615</v>
+        <v>-1.0421</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1.3902</v>
       </c>
       <c r="J11" t="n">
-        <v>0.615</v>
+        <v>-0.875</v>
       </c>
       <c r="K11" t="n">
-        <v>0.615</v>
+        <v>-1.037</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.162</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.2231</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.0052</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.2282</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5599</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.4691</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.1964</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.2727</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. STRIKKER</t>
+          <t>J. VICENTE BOSCH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1330,76 +1330,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1154</v>
+        <v>-5.3179</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5947</v>
+        <v>-3.1145</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7101</v>
+        <v>-2.2036</v>
       </c>
       <c r="G12" t="n">
-        <v>0.452</v>
+        <v>-1.5541</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3451</v>
+        <v>-1.6384</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1069</v>
+        <v>0.08429999999999993</v>
       </c>
       <c r="J12" t="n">
-        <v>0.316</v>
+        <v>-1.5505</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3485</v>
+        <v>-0.951</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0325</v>
+        <v>-0.5995</v>
       </c>
       <c r="M12" t="n">
-        <v>0.136</v>
+        <v>-0.003599999999999992</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0034</v>
+        <v>-0.6874</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1394</v>
+        <v>0.6838</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.39</v>
+        <v>-1.5599</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9749</v>
+        <v>-1.9499</v>
       </c>
       <c r="R12" t="n">
-        <v>0.585</v>
+        <v>0.39</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0533</v>
+        <v>0.5675</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.1074</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0109</v>
+        <v>0.4602</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.7716</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-3.0502</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>V. MUNOZ QUINONES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1408,76 +1408,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7927999999999999</v>
+        <v>-6.4806</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6284</v>
+        <v>-2.833</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8356</v>
+        <v>-3.6477</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3481</v>
+        <v>-2.4818</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0421</v>
+        <v>-1.1066</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3902</v>
+        <v>-1.3752</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.875</v>
+        <v>-2.0802</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.037</v>
+        <v>0.4233</v>
       </c>
       <c r="L13" t="n">
-        <v>0.162</v>
+        <v>-2.5035</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2231</v>
+        <v>-0.4015</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0052</v>
+        <v>-1.5299</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2282</v>
+        <v>1.1283</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.39</v>
+        <v>2.5347</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9499</v>
+        <v>-2.3398</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5599</v>
+        <v>4.8746</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4691</v>
+        <v>-1.4279</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1964</v>
+        <v>-1.1316</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2727</v>
+        <v>-0.2964</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2201</v>
+        <v>-5.1058</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.7187</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2201</v>
+        <v>-7.824599999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. VICENTE BOSCH</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1486,225 +1486,69 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.3179</v>
+        <v>45.72760000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.1145</v>
+        <v>9.341700000000008</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2036</v>
+        <v>36.3857</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5541</v>
+        <v>42.9599</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.6384</v>
+        <v>14.5923</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08429999999999993</v>
+        <v>28.3676</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.5505</v>
+        <v>33.08540000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.951</v>
+        <v>19.3381</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5995</v>
+        <v>13.7473</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.003599999999999992</v>
+        <v>9.874499999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6874</v>
+        <v>-4.7461</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6838</v>
+        <v>14.6203</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5599</v>
+        <v>-9.749300000000002</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9499</v>
+        <v>-74.0947</v>
       </c>
       <c r="R14" t="n">
-        <v>0.39</v>
+        <v>64.3456</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5675</v>
+        <v>8.151499999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1074</v>
+        <v>6.809499999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4602</v>
+        <v>1.341899999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.7716</v>
+        <v>4.364999999999997</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2786</v>
+        <v>43.54059999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.0502</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>V. MUNOZ QUINONES</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-7.6956</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-4.048</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-3.6477</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-3.6968</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-1.1066</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-2.5902</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-3.2953</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.4233</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-3.7185</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-0.4015</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-1.5299</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.1283</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.5347</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-2.3398</v>
-      </c>
-      <c r="R15" t="n">
-        <v>4.8746</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-1.4279</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-1.1316</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-0.2964</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-5.1058</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.7187</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-7.824599999999999</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>45.72760000000002</v>
-      </c>
-      <c r="E16" t="n">
-        <v>9.341700000000008</v>
-      </c>
-      <c r="F16" t="n">
-        <v>36.3857</v>
-      </c>
-      <c r="G16" t="n">
-        <v>42.9599</v>
-      </c>
-      <c r="H16" t="n">
-        <v>14.5922</v>
-      </c>
-      <c r="I16" t="n">
-        <v>28.3676</v>
-      </c>
-      <c r="J16" t="n">
-        <v>33.0853</v>
-      </c>
-      <c r="K16" t="n">
-        <v>19.3381</v>
-      </c>
-      <c r="L16" t="n">
-        <v>13.7473</v>
-      </c>
-      <c r="M16" t="n">
-        <v>9.874499999999999</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-4.7461</v>
-      </c>
-      <c r="O16" t="n">
-        <v>14.6203</v>
-      </c>
-      <c r="P16" t="n">
-        <v>-9.749300000000002</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-74.0947</v>
-      </c>
-      <c r="R16" t="n">
-        <v>64.3456</v>
-      </c>
-      <c r="S16" t="n">
-        <v>8.151499999999999</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6.809499999999998</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.341899999999999</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.364999999999997</v>
-      </c>
-      <c r="W16" t="n">
-        <v>43.54059999999999</v>
-      </c>
-      <c r="X16" t="n">
         <v>-39.17619999999999</v>
       </c>
     </row>
